--- a/data/trans_orig/P36B07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016</t>
+          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>175928</t>
+          <t>179235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225452</t>
+          <t>224424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163314</t>
+          <t>159895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>209705</t>
+          <t>208034</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>349546</t>
+          <t>347944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>418923</t>
+          <t>418063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>107802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145925</t>
+          <t>148207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86188</t>
+          <t>86697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125150</t>
+          <t>123416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201718</t>
+          <t>203537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258309</t>
+          <t>256630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113874</t>
+          <t>112402</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154899</t>
+          <t>155332</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129078</t>
+          <t>129417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172855</t>
+          <t>174695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253077</t>
+          <t>253871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>312660</t>
+          <t>315388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94648</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135160</t>
+          <t>134444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89875</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128384</t>
+          <t>128853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196311</t>
+          <t>196666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250099</t>
+          <t>251497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81795</t>
+          <t>80279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118789</t>
+          <t>117687</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97628</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135932</t>
+          <t>138224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188176</t>
+          <t>188875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242778</t>
+          <t>242175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>238008</t>
+          <t>237742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>293481</t>
+          <t>293742</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229017</t>
+          <t>227318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>284804</t>
+          <t>282972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>477564</t>
+          <t>484427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>563605</t>
+          <t>562195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145771</t>
+          <t>146745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193931</t>
+          <t>197228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151194</t>
+          <t>149312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202645</t>
+          <t>201318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308419</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>376681</t>
+          <t>377741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190223</t>
+          <t>192020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>245237</t>
+          <t>245271</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>196058</t>
+          <t>195177</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248942</t>
+          <t>247928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>401273</t>
+          <t>399720</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>479877</t>
+          <t>476193</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164668</t>
+          <t>165442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215158</t>
+          <t>214085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195583</t>
+          <t>190162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247243</t>
+          <t>245994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>373413</t>
+          <t>369653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>444780</t>
+          <t>446175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149909</t>
+          <t>152684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202096</t>
+          <t>202459</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145892</t>
+          <t>145685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194376</t>
+          <t>193043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>311255</t>
+          <t>309555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>378993</t>
+          <t>382183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141594</t>
+          <t>140614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187631</t>
+          <t>187785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126930</t>
+          <t>125656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170434</t>
+          <t>172110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>274721</t>
+          <t>277276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341122</t>
+          <t>340271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131299</t>
+          <t>132202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178795</t>
+          <t>179221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>131134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175780</t>
+          <t>175794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275236</t>
+          <t>277807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340041</t>
+          <t>342780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164157</t>
+          <t>164486</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211830</t>
+          <t>211613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>160486</t>
+          <t>158498</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>209958</t>
+          <t>209169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>339924</t>
+          <t>338449</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>408357</t>
+          <t>406757</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119000</t>
+          <t>119041</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163987</t>
+          <t>163920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>128981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173154</t>
+          <t>173316</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>260327</t>
+          <t>258498</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>323205</t>
+          <t>321470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87617</t>
+          <t>87261</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128441</t>
+          <t>127008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127927</t>
+          <t>125162</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>174851</t>
+          <t>170698</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>227810</t>
+          <t>226738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>285922</t>
+          <t>288345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172045</t>
+          <t>172652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222345</t>
+          <t>223027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223891</t>
+          <t>222349</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>278735</t>
+          <t>279067</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405653</t>
+          <t>408859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>483791</t>
+          <t>486337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164552</t>
+          <t>165077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215659</t>
+          <t>210537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>182313</t>
+          <t>181905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>236850</t>
+          <t>238436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>361222</t>
+          <t>359636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>433914</t>
+          <t>432270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164041</t>
+          <t>166181</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>210978</t>
+          <t>213554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>168085</t>
+          <t>168779</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219473</t>
+          <t>220172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>344508</t>
+          <t>343851</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>419590</t>
+          <t>415426</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141611</t>
+          <t>140176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191050</t>
+          <t>188363</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>141324</t>
+          <t>140469</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>189978</t>
+          <t>191180</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>293088</t>
+          <t>295651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>364221</t>
+          <t>360788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>170200</t>
+          <t>168349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>216813</t>
+          <t>216413</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>197682</t>
+          <t>196704</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>252671</t>
+          <t>249224</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>378020</t>
+          <t>377680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>453918</t>
+          <t>451362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>775499</t>
+          <t>776595</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>878716</t>
+          <t>876645</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>787647</t>
+          <t>783952</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>888042</t>
+          <t>884012</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1586906</t>
+          <t>1593063</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1726097</t>
+          <t>1726593</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>589303</t>
+          <t>591922</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>682242</t>
+          <t>683327</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>593346</t>
+          <t>590805</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>689326</t>
+          <t>686741</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1208315</t>
+          <t>1211457</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1336252</t>
+          <t>1336381</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>677767</t>
+          <t>672162</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>774753</t>
+          <t>770752</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>696186</t>
+          <t>699403</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>798057</t>
+          <t>796983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1407294</t>
+          <t>1398045</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1542958</t>
+          <t>1537869</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>565913</t>
+          <t>563536</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>653903</t>
+          <t>655116</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>593804</t>
+          <t>593319</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>688247</t>
+          <t>685737</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1180480</t>
+          <t>1188773</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1311687</t>
+          <t>1323789</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>529160</t>
+          <t>531729</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>617529</t>
+          <t>622322</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>608648</t>
+          <t>609319</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>702763</t>
+          <t>704789</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1169030</t>
+          <t>1161420</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1297017</t>
+          <t>1295944</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>179235</t>
+          <t>179145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224424</t>
+          <t>226517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159895</t>
+          <t>161771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208034</t>
+          <t>207695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>347944</t>
+          <t>350845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>418063</t>
+          <t>419794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107802</t>
+          <t>104648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148207</t>
+          <t>145119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86697</t>
+          <t>87191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123416</t>
+          <t>124124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203537</t>
+          <t>202023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256630</t>
+          <t>258364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112402</t>
+          <t>110911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155332</t>
+          <t>153398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129417</t>
+          <t>128570</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174695</t>
+          <t>173260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253871</t>
+          <t>249643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>315388</t>
+          <t>310867</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94271</t>
+          <t>93189</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134444</t>
+          <t>132725</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90667</t>
+          <t>90773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128853</t>
+          <t>128448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196666</t>
+          <t>194237</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251497</t>
+          <t>250573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80279</t>
+          <t>81056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117687</t>
+          <t>117385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98042</t>
+          <t>97086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138224</t>
+          <t>135195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188875</t>
+          <t>185656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242175</t>
+          <t>240275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237742</t>
+          <t>239095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>293742</t>
+          <t>294738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227318</t>
+          <t>226893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>282972</t>
+          <t>284795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>484427</t>
+          <t>477676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>562195</t>
+          <t>563444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146745</t>
+          <t>146641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197228</t>
+          <t>193718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149312</t>
+          <t>150919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201318</t>
+          <t>201571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>307871</t>
+          <t>307173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377741</t>
+          <t>376899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>192020</t>
+          <t>192826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>245271</t>
+          <t>242802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>195177</t>
+          <t>189652</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>247928</t>
+          <t>245802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>399720</t>
+          <t>402209</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>476193</t>
+          <t>479421</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165442</t>
+          <t>163699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214085</t>
+          <t>212428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190162</t>
+          <t>192312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245994</t>
+          <t>247007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369653</t>
+          <t>370082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446175</t>
+          <t>443733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152684</t>
+          <t>153837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202459</t>
+          <t>203438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145685</t>
+          <t>145311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193043</t>
+          <t>194820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>309555</t>
+          <t>311371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>382183</t>
+          <t>381333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140614</t>
+          <t>141115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187785</t>
+          <t>188083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125656</t>
+          <t>124172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172110</t>
+          <t>168882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>277276</t>
+          <t>276757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340271</t>
+          <t>338644</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132202</t>
+          <t>131648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>179221</t>
+          <t>179089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131134</t>
+          <t>130540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175794</t>
+          <t>175397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277807</t>
+          <t>274832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342780</t>
+          <t>339899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164486</t>
+          <t>163377</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211613</t>
+          <t>212820</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158498</t>
+          <t>161444</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>209169</t>
+          <t>212047</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>338449</t>
+          <t>338158</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>406757</t>
+          <t>406700</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119041</t>
+          <t>121005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163920</t>
+          <t>166365</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128981</t>
+          <t>129824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173316</t>
+          <t>172704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>258498</t>
+          <t>261057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>321470</t>
+          <t>324542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87261</t>
+          <t>87831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127008</t>
+          <t>126227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125162</t>
+          <t>124574</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170698</t>
+          <t>169191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>226738</t>
+          <t>227721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288345</t>
+          <t>286807</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172652</t>
+          <t>172789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>223027</t>
+          <t>223062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,47 +2791,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>248830</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>220827</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>276808</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>24,03%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>248830</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>222349</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>279067</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408859</t>
+          <t>413484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>486337</t>
+          <t>488752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165077</t>
+          <t>165024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210537</t>
+          <t>213578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181905</t>
+          <t>181317</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>238436</t>
+          <t>235213</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>359636</t>
+          <t>360803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>432270</t>
+          <t>430556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>166181</t>
+          <t>161788</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213554</t>
+          <t>211823</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>168779</t>
+          <t>166851</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>220172</t>
+          <t>220434</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>343851</t>
+          <t>344070</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>415426</t>
+          <t>415799</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140176</t>
+          <t>143678</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188363</t>
+          <t>190227</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140469</t>
+          <t>141505</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>191180</t>
+          <t>187692</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>295651</t>
+          <t>296938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>360788</t>
+          <t>362647</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>168349</t>
+          <t>169016</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>216413</t>
+          <t>216839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>196704</t>
+          <t>197196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>249224</t>
+          <t>250662</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>377680</t>
+          <t>377967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>451362</t>
+          <t>450697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>776595</t>
+          <t>775157</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>876645</t>
+          <t>872957</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>783952</t>
+          <t>778738</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>884012</t>
+          <t>880635</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1593063</t>
+          <t>1581904</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1726593</t>
+          <t>1736188</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>591922</t>
+          <t>587945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>683327</t>
+          <t>679092</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>590805</t>
+          <t>599802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>686741</t>
+          <t>690104</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1211457</t>
+          <t>1208763</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1336381</t>
+          <t>1341339</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>672162</t>
+          <t>678100</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>770752</t>
+          <t>774882</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>699403</t>
+          <t>699012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>796983</t>
+          <t>796669</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1398045</t>
+          <t>1403557</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1537869</t>
+          <t>1537875</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>563536</t>
+          <t>567732</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>655116</t>
+          <t>654526</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>593319</t>
+          <t>596082</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>685737</t>
+          <t>688363</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1188773</t>
+          <t>1185035</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1323789</t>
+          <t>1318546</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>531729</t>
+          <t>531216</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>622322</t>
+          <t>619386</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>609319</t>
+          <t>612804</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>704789</t>
+          <t>705048</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1161420</t>
+          <t>1168449</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1295944</t>
+          <t>1299154</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
